--- a/Master/2193r1/2193r1 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2193r1/2193r1 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1194,402 +1194,522 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>5.128</v>
+        <v>4.243</v>
       </c>
       <c r="B38" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.8404</v>
+        <v>3.7704</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>-0.2307</v>
+        <v>-1.9504</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>7.227</v>
+        <v>1.246</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3.8517</v>
+        <v>3.7736</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.1337</v>
+        <v>-2.3076</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.003</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>4.129</v>
+        <v>3.244</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>3.906</v>
+        <v>3.7752</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-0.3631</v>
+        <v>-2.0424</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0137</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>3.13</v>
+        <v>6.241</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3.9587</v>
+        <v>3.7774</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.491</v>
+        <v>-1.6406</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0134</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>6.229</v>
+        <v>5.242</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3.968</v>
+        <v>3.7777</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-0.3529</v>
+        <v>-1.7833</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.005</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>2.131</v>
+        <v>2.245</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4.0306</v>
+        <v>3.7787</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.6352</v>
+        <v>-2.1028</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.01</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>1.132</v>
+        <v>5.128</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>4.0659</v>
+        <v>3.8404</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-0.7639</v>
+        <v>-0.2307</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0105</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>4.231</v>
+        <v>7.227</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>4.0705</v>
+        <v>3.8517</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.6113</v>
+        <v>-0.1337</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0043</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>7.133</v>
+        <v>4.129</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>4.1253</v>
+        <v>3.906</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-0.665</v>
+        <v>-0.3631</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0069</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>6.134</v>
+        <v>3.13</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>4.149</v>
+        <v>3.9587</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.491</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>2.233</v>
+        <v>6.229</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>4.1529</v>
+        <v>3.968</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-0.8872</v>
+        <v>-0.3529</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>7.234</v>
+        <v>2.131</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>4.1889</v>
+        <v>4.0306</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.8016</v>
+        <v>-0.6352</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>5.135</v>
+        <v>1.132</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>4.1937</v>
+        <v>4.0659</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-0.9547</v>
+        <v>-0.7639</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>4.136</v>
+        <v>4.231</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>4.2155</v>
+        <v>4.0705</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1.0985</v>
+        <v>-0.6113</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.005</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>3.137</v>
+        <v>7.133</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>4.2296</v>
+        <v>4.1253</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-1.2302</v>
+        <v>-0.665</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0032</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>6.236</v>
+        <v>6.134</v>
       </c>
       <c r="B53" s="6" t="n">
         <v>6</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>4.2334</v>
+        <v>4.149</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-1.0601</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0015</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>1.139</v>
+        <v>2.233</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>4.2453</v>
+        <v>4.1529</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-1.4817</v>
+        <v>-0.8872</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>2.138</v>
+        <v>7.234</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>4.2456</v>
+        <v>4.1889</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-1.4144</v>
+        <v>-0.8016</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0011</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
+        <v>5.135</v>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>4.1937</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>-0.9547</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.0052</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>4.136</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>4.2155</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>-1.0985</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>3.137</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>4.2296</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>-1.2302</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>6.236</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>4.2334</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>-1.0601</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0.0015</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>4.2453</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>-1.4817</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>4.2456</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>-1.4144</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.0011</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
         <v>4.238</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B62" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D56" s="7" t="n">
+      <c r="C62" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="7" t="n">
         <v>4.2493</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E62" s="7" t="n">
         <v>-1.3482</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F62" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="E58" s="8" t="inlineStr">
+    <row r="64">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="E59" s="8" t="inlineStr">
+      <c r="F64" s="9" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>1.0444</v>
+      <c r="F65" s="10" t="n">
+        <v>1.0464</v>
       </c>
     </row>
   </sheetData>
